--- a/test-reports/2_Appium_Mobile_E2E_Test_Report.xlsx
+++ b/test-reports/2_Appium_Mobile_E2E_Test_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>27/8/2026</t>
+    <t>28/10/2026</t>
   </si>
   <si>
     <t>Module Tested:</t>
